--- a/data/trans_bre/IP2001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Edad-trans_bre.xlsx
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,0</t>
+          <t>-2,88; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>0,0; 11,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,24</t>
+          <t>-2,79; 2,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 6,36</t>
+          <t>-2,43; 5,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,61</t>
+          <t>-2,16; 6,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,77</t>
+          <t>-5,47; 1,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 121,48</t>
+          <t>-49,39; 95,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 124,52</t>
+          <t>-28,53; 123,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 102,44</t>
+          <t>-27,13; 109,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,81; 67,8</t>
+          <t>-75,09; 63,41</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 6,74</t>
+          <t>-6,14; 7,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 8,29</t>
+          <t>-4,22; 9,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 5,31</t>
+          <t>-7,22; 5,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 4,04</t>
+          <t>-4,45; 4,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 66,37</t>
+          <t>-37,58; 72,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 79,9</t>
+          <t>-26,99; 92,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 37,97</t>
+          <t>-36,94; 39,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,08; 106,44</t>
+          <t>-52,65; 120,76</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 6,76</t>
+          <t>-4,21; 6,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 1,34</t>
+          <t>-10,78; 0,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 7,81</t>
+          <t>-4,0; 7,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,43; -0,07</t>
+          <t>-7,13; 0,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 72,69</t>
+          <t>-27,85; 76,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,65; 12,26</t>
+          <t>-58,87; 8,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 103,47</t>
+          <t>-29,74; 107,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,28; 0,36</t>
+          <t>-74,69; 11,07</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,96</t>
+          <t>-1,99; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,38</t>
+          <t>-2,55; 2,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,39</t>
+          <t>-1,68; 3,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,54</t>
+          <t>-3,89; 0,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 43,16</t>
+          <t>-21,89; 40,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 29,64</t>
+          <t>-23,8; 34,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 40,05</t>
+          <t>-15,82; 41,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 12,44</t>
+          <t>-52,81; 12,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Edad-trans_bre.xlsx
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,52</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,8</t>
+          <t>-2,59; 3,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 5,84</t>
+          <t>-2,05; 6,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 6,01</t>
+          <t>-2,3; 6,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 1,68</t>
+          <t>-5,57; 1,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,39; 95,65</t>
+          <t>-46,46; 108,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 123,55</t>
+          <t>-26,59; 139,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 109,89</t>
+          <t>-27,67; 117,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,09; 63,41</t>
+          <t>-74,19; 57,8</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 7,4</t>
+          <t>-6,23; 6,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,12</t>
+          <t>-4,17; 8,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 5,31</t>
+          <t>-7,46; 4,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 4,48</t>
+          <t>-5,02; 3,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,58; 72,98</t>
+          <t>-36,32; 66,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 92,06</t>
+          <t>-26,37; 80,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 39,33</t>
+          <t>-36,76; 35,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,65; 120,76</t>
+          <t>-56,89; 89,35</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 6,69</t>
+          <t>-3,89; 6,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 0,96</t>
+          <t>-10,3; 0,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 7,94</t>
+          <t>-2,89; 8,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 0,27</t>
+          <t>-7,11; 0,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 76,16</t>
+          <t>-27,25; 70,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,87; 8,42</t>
+          <t>-57,5; 6,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 107,66</t>
+          <t>-24,25; 120,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,69; 11,07</t>
+          <t>-73,83; 2,98</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,86</t>
+          <t>-2,12; 2,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,8</t>
+          <t>-2,93; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,52</t>
+          <t>-1,77; 3,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,51</t>
+          <t>-3,78; 0,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 40,7</t>
+          <t>-23,13; 38,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 34,93</t>
+          <t>-26,33; 30,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 41,19</t>
+          <t>-16,08; 39,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 12,39</t>
+          <t>-53,2; 7,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-3,61; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,31</t>
+          <t>0,0; 11,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-33,94%</t>
+          <t>-36,65%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,14</t>
+          <t>-2,72; 3,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,07</t>
+          <t>-1,94; 6,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 6,17</t>
+          <t>-2,02; 5,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 1,66</t>
+          <t>-5,86; 1,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,46; 108,33</t>
+          <t>-46,37; 121,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 139,3</t>
+          <t>-24,62; 124,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 117,56</t>
+          <t>-25,45; 102,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 57,8</t>
+          <t>-75,76; 59,27</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-4,81%</t>
+          <t>-8,06%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 6,78</t>
+          <t>-6,19; 6,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 8,17</t>
+          <t>-4,97; 8,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 4,73</t>
+          <t>-7,73; 5,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 3,88</t>
+          <t>-4,91; 4,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,32; 66,28</t>
+          <t>-36,17; 66,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 80,6</t>
+          <t>-29,56; 79,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 35,83</t>
+          <t>-37,36; 37,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-56,89; 89,35</t>
+          <t>-54,41; 102,9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-45,34%</t>
+          <t>-37,89%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 6,7</t>
+          <t>-4,15; 6,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 0,83</t>
+          <t>-10,72; 1,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 8,32</t>
+          <t>-3,28; 7,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 0,13</t>
+          <t>-6,66; 0,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 70,1</t>
+          <t>-30,7; 72,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,5; 6,05</t>
+          <t>-57,65; 12,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 120,64</t>
+          <t>-29,2; 103,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,83; 2,98</t>
+          <t>-70,02; 12,13</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-27,53%</t>
+          <t>-25,49%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,7</t>
+          <t>-2,07; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,44</t>
+          <t>-2,77; 2,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,35</t>
+          <t>-1,81; 3,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,4</t>
+          <t>-3,78; 0,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 38,11</t>
+          <t>-22,38; 43,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 30,69</t>
+          <t>-25,37; 29,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 39,56</t>
+          <t>-16,83; 40,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 7,53</t>
+          <t>-50,31; 12,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,26 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.6960515971400114</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.320876387229013</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +646,146 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,61; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,45</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>-3.612691264407945</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.45198273962549</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,05</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,92%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-36,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,72; 3,24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,94; 6,36</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,02; 5,61</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,86; 1,78</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-46,37; 121,48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-24,62; 124,52</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-25,45; 102,44</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-75,76; 59,27</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.06863329140146465</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.000810487670774</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.537538241911635</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.048406756283948</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.01548812463583444</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.309166662875503</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2185221488837683</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3665126151960591</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-6,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-8,06%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.715530802431005</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.943810281296673</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.017374390125184</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.858933838380766</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4637031265749657</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2461612333252072</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.254473043705643</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7576206910519966</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,19; 6,74</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,97; 8,29</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,73; 5,31</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,91; 4,09</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-36,17; 66,37</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-29,56; 79,9</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-37,36; 37,97</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-54,41; 102,9</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.244869286999759</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.3565576357011</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.607365683253639</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.776647798367415</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.214834353817801</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.245151719578287</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.02444140660387</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.5926846140198068</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +793,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-4,89</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,38</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-31,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-37,89%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.2857603176074031</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.917290832981513</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.131792862609277</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.5515815501680523</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.02100642464895081</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1463458642812423</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.06665556170012933</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.08063733461642146</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,15; 6,76</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-10,72; 1,34</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,28; 7,81</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,66; 0,49</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-30,7; 72,69</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-57,65; 12,26</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-29,2; 103,47</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-70,02; 12,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.187895193296602</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.972367186363088</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.727769333506498</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.905066865550426</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3617353780510404</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.29559594478524</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3735569421141793</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5441086868359553</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.737154021030406</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.28735247715507</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.309641600160591</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.089120735160837</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.6637170701939958</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7989635424610189</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3796788005149406</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.029017492672705</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.216460800641821</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-4.890135599965093</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.377327093464181</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.609304904023388</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1024990181583721</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3130638146681572</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2381549161013173</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3788557197468753</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.151684934889188</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-10.72456282116355</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.281411224229804</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.657555544910383</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3070124934234064</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5764549551782386</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2920470685007079</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7002470813476062</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.759477975337505</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.343230589951925</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.805850391078677</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.4870631125966757</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7269376249666615</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1226119903548012</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.034744964244968</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.121259438813946</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,58</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,88%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-25,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 2,96</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,77; 2,38</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 3,39</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 0,59</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-22,38; 43,16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-25,37; 29,64</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-16,83; 40,05</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-50,31; 12,02</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.4578927926325096</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.08242609409939011</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.787220284522247</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.575185453507531</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.05735881607826794</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.008758578226509476</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.08104671430221705</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2548705344317573</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.074660562929395</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.772867515356981</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.812628028949577</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.775262712553534</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2238291563756585</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2536738930799342</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1682623284933286</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.5031394316382755</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.961332757354558</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.384031847157595</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.393424939764511</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.5918090908483898</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.431626800333319</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2964387090194573</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.400546664399573</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1202315819598125</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1091,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
